--- a/mistral_translate_work/split_by_prompt/excel/name_title/lang_multi_text/lang_multi_text__name_title__part_0009.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/name_title/lang_multi_text/lang_multi_text__name_title__part_0009.xlsx
@@ -574,7 +574,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Grandma Jue</t>
+          <t>Bà Jue</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -1414,7 +1414,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Hotel</t>
+          <t>Khách Sạn</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Mingming</t>
+          <t>Minh Minh</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>NPC Test</t>
+          <t>Kiểm tra NPC</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -1764,7 +1764,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>NPC Test 2</t>
+          <t>Kiểm tra NPC 2</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1904,7 +1904,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Pinwen</t>
+          <t>Pinwên</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -2254,7 +2254,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Screen Placeholder</t>
+          <t>Vị Trí Màn Hình Trống</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Shuncai</t>
+          <t>Thuận Tài</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -2534,7 +2534,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Storyteller</t>
+          <t>Người Kể Chuyện</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -2744,7 +2744,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Time Placeholder</t>
+          <t>Đánh Dấu Thời Gian</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -2814,7 +2814,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>Tacet Field (NPC) Test</t>
+          <t>Bài Kiểm Tra (NPC) Tổ Tacet</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>Tacet Field Test</t>
+          <t>Bài Kiểm Tra Tổ Tacet</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>Tacet Field Test 2</t>
+          <t>Bài Kiểm Tra Tổ Tacet 2</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -3164,7 +3164,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>Jiu</t>
+          <t>Cửu</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -3234,7 +3234,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>Xieyang</t>
+          <t>Tạ Dương</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -3304,7 +3304,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>Xinyi</t>
+          <t>Tân Nghi</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -3374,7 +3374,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>Xuxu</t>
+          <t>Tú Tú</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -3934,7 +3934,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>Uncle Yun</t>
+          <t>Chú Vân</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>Zhuyi</t>
+          <t>Chủ Ý</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>Vị trí Tacet Field Crownless chính</t>
+          <t>Vị trí Tổ Tacet Crownless chính</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -4354,7 +4354,7 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>Tortoise Tacet Field Placeholder</t>
+          <t>Biến thể Tổ Tacet Rùa Địa placeholder</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -4564,7 +4564,7 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>Underground Scaleman Refresh</t>
+          <t>Làm Mới Thợ Săn Dưới Lòng Đất</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -4634,7 +4634,7 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>Vị trí mục tiêu không khả dụng</t>
+          <t>Không xác định được vị trí mục tiêu</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
@@ -4774,7 +4774,7 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>Vị trí mục tiêu không khả dụng</t>
+          <t>Không xác định được vị trí mục tiêu</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
@@ -4984,7 +4984,7 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>Lecture Hall</t>
+          <t>Giảng đường</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
@@ -5054,7 +5054,7 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>Screening Room</t>
+          <t>Phòng Chiếu</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>Lord Wo'air Placeholder</t>
+          <t>Địa Điểm Dự Phòng Lord Wo'air</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
@@ -5404,7 +5404,7 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>Test Placeholder</t>
+          <t>Vị trí thử nghiệm</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
@@ -5474,7 +5474,7 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>Test Placeholder 3</t>
+          <t>Vị trí thử nghiệm 3</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
@@ -5614,7 +5614,7 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>Inferno Rider Tacet Field Placeholder</t>
+          <t>Vị Trí Tổ Tacet Kỵ Sĩ Hỏa Ngục</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
@@ -5754,7 +5754,7 @@
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>Upphaf Life Chamber</t>
+          <t>Buồng Sinh Mệnh Upphaf</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
@@ -5824,7 +5824,7 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>Qichi Village Tacet Field</t>
+          <t>Tổ Tacet Làng Qichi</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
@@ -6244,7 +6244,7 @@
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>Lampylumen Myriad Placeholder</t>
+          <t>Vị trí Lampylumen Myriad</t>
         </is>
       </c>
       <c r="N83" t="inlineStr">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>Scaleman Tacet Field Placeholder</t>
+          <t>Vùng Tổ Tacet Scaleman (Placeholder)</t>
         </is>
       </c>
       <c r="N86" t="inlineStr">
@@ -6524,7 +6524,7 @@
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>New Arrival Đến Thành Phố Lớn</t>
+          <t>Vị Khách Mới Đến Thành Phố Lớn</t>
         </is>
       </c>
       <c r="N87" t="inlineStr">
@@ -6664,7 +6664,7 @@
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>New Arrival Đến Thành Phố Lớn</t>
+          <t>Vị Khách Mới Đến Thành Phố Lớn</t>
         </is>
       </c>
       <c r="N89" t="inlineStr">
@@ -6804,7 +6804,7 @@
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>Gladiator Training</t>
+          <t>Huấn Luyện Đấu Sĩ</t>
         </is>
       </c>
       <c r="N91" t="inlineStr">
@@ -6944,7 +6944,7 @@
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>Gladiator Training</t>
+          <t>Huấn Luyện Đấu Sĩ</t>
         </is>
       </c>
       <c r="N93" t="inlineStr">
@@ -7084,7 +7084,7 @@
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>The Impossible Trial</t>
+          <t>Thử Thách Bất Khả Thi</t>
         </is>
       </c>
       <c r="N95" t="inlineStr">
@@ -7224,7 +7224,7 @@
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>The Impossible Trial</t>
+          <t>Thử Thách Bất Khả Thi</t>
         </is>
       </c>
       <c r="N97" t="inlineStr">
@@ -7364,7 +7364,7 @@
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>Proof of Honor</t>
+          <t>Bằng Chứng Danh Dự</t>
         </is>
       </c>
       <c r="N99" t="inlineStr">
@@ -7434,7 +7434,7 @@
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>At the Summit of Septimont</t>
+          <t>Trên đỉnh Septimont</t>
         </is>
       </c>
       <c r="N100" t="inlineStr">
@@ -7574,7 +7574,7 @@
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>At the Summit of Septimont</t>
+          <t>Trên đỉnh Septimont</t>
         </is>
       </c>
       <c r="N102" t="inlineStr">
@@ -7714,7 +7714,7 @@
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>Defeated Cato</t>
+          <t>Đã đánh bại Cato</t>
         </is>
       </c>
       <c r="N104" t="inlineStr">
@@ -7784,7 +7784,7 @@
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>Trainee Gladiator</t>
+          <t>Võ Sĩ Tập Sự</t>
         </is>
       </c>
       <c r="N105" t="inlineStr">
@@ -7854,7 +7854,7 @@
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>Succesfully defeated the Lion Beast</t>
+          <t>Đã đánh bại thành công Lion Beast</t>
         </is>
       </c>
       <c r="N106" t="inlineStr">
@@ -7924,7 +7924,7 @@
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>Fearless Trialbearer</t>
+          <t>Người gánh vác thử thách không sợ hãi</t>
         </is>
       </c>
       <c r="N107" t="inlineStr">
@@ -7994,7 +7994,7 @@
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>Spared Aridel</t>
+          <t>Đã tha cho Aridel</t>
         </is>
       </c>
       <c r="N108" t="inlineStr">
@@ -8064,7 +8064,7 @@
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>Kiếm Glory</t>
+          <t>Kiếm Vinh Quang</t>
         </is>
       </c>
       <c r="N109" t="inlineStr">
@@ -8204,7 +8204,7 @@
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>Summit of Septimont</t>
+          <t>Đỉnh Septimont</t>
         </is>
       </c>
       <c r="N111" t="inlineStr">
@@ -8274,7 +8274,7 @@
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>Chin Up</t>
+          <t>Ngẩng đầu lên</t>
         </is>
       </c>
       <c r="N112" t="inlineStr">
@@ -8344,7 +8344,7 @@
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>Tough to Swallow</t>
+          <t>Khó mà nuốt trôi</t>
         </is>
       </c>
       <c r="N113" t="inlineStr">
@@ -8414,7 +8414,7 @@
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>Accepting Fate</t>
+          <t>Chấp nhận Số Phận</t>
         </is>
       </c>
       <c r="N114" t="inlineStr">
@@ -8554,7 +8554,7 @@
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>Never Forgotten</t>
+          <t>Không Bao Giờ Quên</t>
         </is>
       </c>
       <c r="N116" t="inlineStr">
@@ -8694,7 +8694,7 @@
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>Imminent Crisis</t>
+          <t>Khủng hoảng cận kề</t>
         </is>
       </c>
       <c r="N118" t="inlineStr">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>Justice and the sword</t>
+          <t>Công Lý và Lưỡi Kiếm</t>
         </is>
       </c>
       <c r="N120" t="inlineStr">
@@ -8974,7 +8974,7 @@
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>Tossing the helmet at nobility</t>
+          <t>Ném mũ bảo hiểm vào giới quý tộc</t>
         </is>
       </c>
       <c r="N122" t="inlineStr">
@@ -9044,7 +9044,7 @@
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>Don't Sully My Hands</t>
+          <t>Đừng để tay tao dính bẩn</t>
         </is>
       </c>
       <c r="N123" t="inlineStr">
@@ -9114,7 +9114,7 @@
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>Forging a great sword</t>
+          <t>Rèn một thanh đại kiếm</t>
         </is>
       </c>
       <c r="N124" t="inlineStr">
@@ -9184,7 +9184,7 @@
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>Proof of Honor</t>
+          <t>Bằng Chứng Danh Dự</t>
         </is>
       </c>
       <c r="N125" t="inlineStr">
@@ -9254,7 +9254,7 @@
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>Establish yourself in Septimont</t>
+          <t>Dừng chân tại Septimont và xây dựng vị thế của mình.</t>
         </is>
       </c>
       <c r="N126" t="inlineStr">
@@ -9394,7 +9394,7 @@
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>Huấn Luyện Combat</t>
+          <t>Huấn Luyện Chiến Đấu</t>
         </is>
       </c>
       <c r="N128" t="inlineStr">
@@ -9534,7 +9534,7 @@
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>Challenging the Trials</t>
+          <t>Thách Đấu Các Phép Thử</t>
         </is>
       </c>
       <c r="N130" t="inlineStr">
@@ -9674,7 +9674,7 @@
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>The Ngày of Crowning</t>
+          <t>Ngày Đăng Quang</t>
         </is>
       </c>
       <c r="N132" t="inlineStr">
@@ -27034,7 +27034,7 @@
       </c>
       <c r="M380" t="inlineStr">
         <is>
-          <t>Weapon Forger</t>
+          <t>Vũ khí Forger</t>
         </is>
       </c>
       <c r="N380" t="inlineStr">
